--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -582,11 +582,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -674,11 +674,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -950,11 +950,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1134,11 +1134,11 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1226,11 +1226,11 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1318,11 +1318,11 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1410,11 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,106 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_Deadline_Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statute_Citation</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -582,31 +604,41 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -674,31 +706,41 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -766,31 +808,41 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -858,31 +910,41 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -950,31 +1012,41 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1042,31 +1114,41 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1134,31 +1216,41 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1226,31 +1318,41 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1318,31 +1420,41 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1410,31 +1522,41 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1502,31 +1624,41 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1726,41 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-14 16:42:31</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Parcel_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Record_Type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -553,92 +568,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>50-43-43-15-06-001-0020</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-TD-004501</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>ANTHONY &amp; GRACE VALENTINE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="b">
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>720 S OCEAN BLVD PALM BEACH FL 33480</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>145000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>29000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>75</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -650,97 +680,112 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-TD-004812</t>
+          <t>4942-12-05-0890</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LUIS &amp; MARIA HERNANDEZ</t>
+          <t>2024-TD-003891</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>MARCUS &amp; HELENA VANDERBILT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="b">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>340 SW 8TH ST MIAMI FL 33130</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>1520 SE 12TH ST FORT LAUDERDALE FL 33316</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>112000</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>138500</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>27700</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>75</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>https://www.miamidadeclerk.gov/</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -752,97 +797,112 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-TD-008912</t>
+          <t>02-3209-018-0240</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+          <t>2024-CA-012874</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F4" t="b">
+          <t>ESTATE OF JULIAN MERCER</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
-        </is>
+      <c r="H4" t="b">
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>92400</v>
-      </c>
-      <c r="K4" t="inlineStr">
+          <t>1440 OCEAN DR APT 402 MIAMI BEACH FL 33139</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Condo / Multi-Family</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>18480</v>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>23000</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>75</v>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -854,97 +914,112 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-TD-001955</t>
+          <t>01-4138-005-0120</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JAMES &amp; LINDA CHEN</t>
+          <t>2024-TD-004812</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>LUIS &amp; MARIA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F5" t="b">
+      <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="b">
+      <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>340 SW 8TH ST MIAMI FL 33130</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>74300</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>112000</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>14860</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>22400</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>75</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://www.myorangeclerk.com/</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -956,97 +1031,112 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-TD-004688</t>
+          <t>182914-4TA000001000020</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ESTATE OF ARTHUR STERLING</t>
+          <t>2024-TD-008912</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
+          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
-        </is>
+      <c r="H6" t="b">
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>68900</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>92400</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>13780</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>18480</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>75</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1058,97 +1148,112 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-TD-001501</t>
+          <t>30-4014-012-0580</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ESTATE OF ELEANOR VANCE</t>
+          <t>2024-CA-014289</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>ESTATE OF VICTORIA CRANE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
-        </is>
+      <c r="H7" t="b">
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>10845 SW 72ND AVE MIAMI FL 33156</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>61800</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>89450</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>12360</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>17890</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>75</v>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1160,97 +1265,112 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-TD-009041</t>
+          <t>5142-28-03-0140</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ESTATE OF HENRY PATTERSON</t>
+          <t>2024-TD-004105</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>ESTATE OF RAYMOND CHANDLER</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
-        </is>
+      <c r="H8" t="b">
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>3840 N 56TH AVE HOLLYWOOD FL 33021</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>54100</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>84200</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>10820</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>16840</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>75</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>https://www.hillsclerk.com/</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1262,97 +1382,112 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-TD-001248</t>
+          <t>00-43-43-05-11-002-0080</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RICHARD HAWKINS</t>
+          <t>2024-CA-006731</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>REBECCA &amp; GERALD MONROE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F9" t="b">
+      <c r="G9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="b">
+      <c r="H9" t="b">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>318 COLONIAL RD WEST PALM BEACH FL 33405</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>48250</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>78250</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>9650</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>15650</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>75</v>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1364,97 +1499,112 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-TD-004990</t>
+          <t>28-23-27-0000-00-015</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EUGENE FITZPATRICK</t>
+          <t>2024-TD-001955</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>JAMES &amp; LINDA CHEN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F10" t="b">
+      <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="b">
+      <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1920 CORAL WAY MIAMI FL 33145</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>43500</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>74300</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>8700</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>14860</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>75</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>https://www.miamidadeclerk.gov/</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1466,97 +1616,112 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-TD-009188</t>
+          <t>00-42-43-27-05-022-0140</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DANIELLE KAUFMAN</t>
+          <t>2024-TD-004688</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F11" t="b">
+          <t>ESTATE OF ARTHUR STERLING</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
-        </is>
+      <c r="H11" t="b">
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>31750</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>68900</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>6350</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>13780</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>75</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>https://www.hillsclerk.com/</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>https://www.mypalmbeachclerk.com/</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1568,97 +1733,112 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-TD-001622</t>
+          <t>4842-18-09-0410</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+          <t>2024-CA-009842</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F12" t="b">
+          <t>ESTATE OF LAWRENCE THORNE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
-        </is>
+      <c r="H12" t="b">
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>4210 NE 22ND AVE LIGHTHOUSE POINT FL 33064</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>29400</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>64800</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>5880</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="n">
+        <v>12960</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>75</v>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1675,92 +1855,1043 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>29-22-30-0000-00-042</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2024-TD-001501</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ESTATE OF ELEANOR VANCE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>61800</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>12360</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>192802-5TB000002000040</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2024-TD-009041</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ESTATE OF HENRY PATTERSON</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>54100</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>10820</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Broward</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4842-35-08-0320</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2024-TD-002980</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PATRICIA &amp; GLENN O'CONNOR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2100 NE 48TH ST POMPANO BEACH FL 33064</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>52700</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>10540</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>29-22-29-0000-00-088</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024-TD-001248</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RICHARD HAWKINS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>48250</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>9650</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01-3122-015-0450</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2024-TD-004990</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EUGENE FITZPATRICK</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1920 CORAL WAY MIAMI FL 33145</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>43500</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Broward</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5041-35-02-0190</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024-CA-011205</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>THOMAS &amp; CLARA WHITFIELD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8920 SW 18TH ST PLANTATION FL 33324</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>41600</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>8320</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>182923-3TC000001000010</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2024-TD-009188</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DANIELLE KAUFMAN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>31750</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>6350</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>28-21-15-0000-00-031</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2024-TD-001622</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>29400</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>5880</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>29-23-35-0000-00-019</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>2024-TD-001844</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>BEATRICE MONTGOMERY</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F13" t="b">
+      <c r="G21" t="b">
         <v>1</v>
       </c>
-      <c r="G13" t="b">
+      <c r="H21" t="b">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>220 W KALEY ST ORLANDO FL 32806</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K21" t="n">
         <v>18900</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M21" t="n">
         <v>3780</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="O13" t="n">
+      <c r="P21" t="n">
         <v>75</v>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13608,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18366,7 +18366,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18732,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 09:56:13</t>
+          <t>2026-10-16 10:17:38</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13608,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18366,7 +18366,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18732,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 10:17:38</t>
+          <t>2026-10-16 10:36:03</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13608,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14828,7 +14828,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16292,7 +16292,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16658,7 +16658,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17390,7 +17390,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17756,7 +17756,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18366,7 +18366,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18732,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -18976,7 +18976,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>
@@ -19708,7 +19708,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-16 10:36:03</t>
+          <t>2026-10-16 12:30:07</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7759,12 +7759,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8613,12 +8613,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8735,12 +8735,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9223,12 +9223,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9467,12 +9467,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10443,12 +10443,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10565,12 +10565,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10687,12 +10687,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -10931,12 +10931,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11053,12 +11053,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11297,12 +11297,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11419,12 +11419,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11541,12 +11541,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11663,12 +11663,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11907,12 +11907,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12029,12 +12029,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12151,12 +12151,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12395,12 +12395,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12517,12 +12517,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12639,12 +12639,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12761,12 +12761,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -12883,12 +12883,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13127,12 +13127,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13493,12 +13493,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13615,12 +13615,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13737,12 +13737,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13859,12 +13859,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -13981,12 +13981,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14103,12 +14103,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14225,12 +14225,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14347,12 +14347,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14469,12 +14469,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14713,12 +14713,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14835,12 +14835,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15079,12 +15079,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15201,12 +15201,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15323,12 +15323,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15445,12 +15445,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15567,12 +15567,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15689,12 +15689,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15811,12 +15811,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -15933,12 +15933,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16055,12 +16055,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16299,12 +16299,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16421,12 +16421,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16543,12 +16543,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16787,12 +16787,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -16909,12 +16909,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17031,12 +17031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17153,12 +17153,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17397,12 +17397,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17519,12 +17519,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17641,12 +17641,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17763,12 +17763,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -17885,12 +17885,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18129,12 +18129,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18251,12 +18251,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18373,12 +18373,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18495,12 +18495,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18617,12 +18617,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18739,12 +18739,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18861,12 +18861,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -18983,12 +18983,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:30Z</t>
+          <t>2026-10-18T11:01:41Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19105,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -19227,12 +19227,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -19471,12 +19471,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -19593,12 +19593,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>
@@ -19715,12 +19715,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-17T10:41:31Z</t>
+          <t>2026-10-18T11:01:42Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-17 10:41:43</t>
+          <t>2026-10-18 11:01:54</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7759,12 +7759,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7881,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8613,12 +8613,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8735,12 +8735,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9223,12 +9223,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9467,12 +9467,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10443,12 +10443,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10565,12 +10565,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10687,12 +10687,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -10931,12 +10931,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11053,12 +11053,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11175,12 +11175,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11297,12 +11297,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11419,12 +11419,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11541,12 +11541,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11663,12 +11663,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -11907,12 +11907,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12029,12 +12029,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12151,12 +12151,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12273,12 +12273,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12395,12 +12395,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12517,12 +12517,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12639,12 +12639,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12761,12 +12761,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -12883,12 +12883,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13127,12 +13127,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13493,12 +13493,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13615,12 +13615,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13737,12 +13737,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13859,12 +13859,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -13981,12 +13981,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14103,12 +14103,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14225,12 +14225,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14347,12 +14347,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14469,12 +14469,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14713,12 +14713,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14835,12 +14835,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15079,12 +15079,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15201,12 +15201,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15323,12 +15323,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15445,12 +15445,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15567,12 +15567,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15689,12 +15689,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15811,12 +15811,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -15933,12 +15933,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16055,12 +16055,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16299,12 +16299,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16421,12 +16421,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16543,12 +16543,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16665,12 +16665,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16787,12 +16787,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -16909,12 +16909,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17031,12 +17031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17153,12 +17153,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17397,12 +17397,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17519,12 +17519,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17641,12 +17641,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17763,12 +17763,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -17885,12 +17885,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18129,12 +18129,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18251,12 +18251,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18373,12 +18373,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18495,12 +18495,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18617,12 +18617,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18739,12 +18739,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18861,12 +18861,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -18983,12 +18983,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:41Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19105,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -19227,12 +19227,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -19471,12 +19471,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -19593,12 +19593,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>
@@ -19715,12 +19715,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-18T11:01:42Z</t>
+          <t>2026-10-19T13:10:34Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-18 11:01:54</t>
+          <t>2026-10-19 13:10:46</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB158"/>
+  <dimension ref="A1:AB160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CA-008975</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-008975</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CP-002386</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-002386</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CP-002619</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-002619</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-002515</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-002515</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CP-000212</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-000212</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=15-CA-001463</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=15-CA-001463</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CP-002439</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-002439</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=14-CC-036459</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=14-CC-036459</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CP-004050</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-004050</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-011013</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-011013</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CP-002815</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-002815</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=19-CP-000093</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-000093</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CP-001816</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-001816</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CP-002495</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-002495</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-053397</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-053397</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=17-CA-001731</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=17-CA-001731</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CP-000236</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-000236</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=15-CP-001594</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=15-CP-001594</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-025679</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-025679</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=19-CP-000331</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-000331</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-008539</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-008539</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CC-012552</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CC-012552</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=14-CP-001685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=14-CP-001685</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9223,12 +9223,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-040872</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-040872</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -9467,12 +9467,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=89-CP-000329</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=89-CP-000329</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=18-CP-000981</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=18-CP-000981</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9711,12 +9711,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=13-CP-000149</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=13-CP-000149</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CP-001829</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-001829</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CC-090753</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CC-090753</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-033697</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033697</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-044373</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-044373</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-021712</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-021712</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-033927</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033927</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-038836</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038836</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -10687,12 +10687,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CC-004204</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-004204</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P88" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-042698</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042698</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-030765</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-030765</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-036800</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036800</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-046797</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-046797</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-036196</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036196</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CP-002379</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-002379</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-047045</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047045</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12151,12 +12151,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-031087</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-031087</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-041455</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041455</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -12395,12 +12395,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -12517,12 +12517,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CP-003171</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-003171</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-022913</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-022913</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-057250</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-057250</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-003139</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-003139</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -13127,12 +13127,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-040382</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-040382</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-033877</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033877</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-036763</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036763</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -13493,12 +13493,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P108" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-018307</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-018307</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P109" t="inlineStr"/>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-045915</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-045915</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P110" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-015407</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-015407</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -13859,12 +13859,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-028992</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-028992</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P112" t="inlineStr"/>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-045789</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-045789</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -14103,12 +14103,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P113" t="inlineStr"/>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-054158</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-054158</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -14225,12 +14225,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P114" t="inlineStr"/>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-008441</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-008441</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P115" t="inlineStr"/>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-048032</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048032</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P116" t="inlineStr"/>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CP-001543</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-001543</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14661,7 +14661,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-025860</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-025860</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P118" t="inlineStr"/>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-020536</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-020536</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -14835,12 +14835,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14858,12 +14858,12 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>26-CC-033916</t>
+          <t>26-CC-042880</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leach, Amanda</t>
+          <t>JOHNSON, SUZETH HIBBERT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -14888,7 +14888,7 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>3988</v>
+        <v>4000</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="M119" t="n">
-        <v>797.6</v>
+        <v>800</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
@@ -14922,17 +14922,17 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-033916</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042880</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-033916</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-042880</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14980,12 +14980,12 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>24-CC-066151</t>
+          <t>26-CC-033916</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lyte, Christopher</t>
+          <t>Leach, Amanda</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>3900</v>
+        <v>3988</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>780</v>
+        <v>797.6</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P120" t="inlineStr"/>
@@ -15044,17 +15044,17 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CC-066151</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033916</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-066151</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-033916</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -15079,12 +15079,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15102,12 +15102,12 @@
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>26-CC-038737</t>
+          <t>24-CC-066151</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MATHIS, MEGAN MARIE</t>
+          <t>Lyte, Christopher</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -15132,7 +15132,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>3815.2</v>
+        <v>3900</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>763.04</v>
+        <v>780</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
@@ -15166,17 +15166,17 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-038737</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-066151</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-038737</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-066151</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15224,12 +15224,12 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>26-CC-042880</t>
+          <t>26-CC-038737</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>JOHNSON, SUZETH HIBBERT</t>
+          <t>MATHIS, MEGAN MARIE</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -15254,7 +15254,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>3800</v>
+        <v>3815.2</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>760</v>
+        <v>763.04</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P122" t="inlineStr"/>
@@ -15288,17 +15288,17 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-042880</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038737</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-042880</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-038737</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -15323,12 +15323,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P123" t="inlineStr"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-046372</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046372</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P124" t="inlineStr"/>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-048087</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048087</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -15567,12 +15567,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-048006</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048006</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P126" t="inlineStr"/>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-046665</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046665</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
@@ -15811,12 +15811,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-011115</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-011115</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -15933,12 +15933,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-046414</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046414</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
@@ -16055,12 +16055,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P129" t="inlineStr"/>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-042617</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042617</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P130" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-040526</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-040526</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P131" t="inlineStr"/>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=23-CP-002624</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-002624</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
@@ -16421,12 +16421,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16444,12 +16444,12 @@
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>26-CC-038515</t>
+          <t>26-CC-046381</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>GLOSTER, STANLEY</t>
+          <t>Mujahid, Qudeja</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>3206.05</v>
+        <v>3270.12</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>641.21</v>
+        <v>654.02</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P132" t="inlineStr"/>
@@ -16508,17 +16508,17 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-038515</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046381</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-038515</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-046381</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
@@ -16543,12 +16543,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16566,12 +16566,12 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>19-CP-002176</t>
+          <t>26-CC-038515</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LARA, PABLO A</t>
+          <t>GLOSTER, STANLEY</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -16596,7 +16596,7 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>3169.22</v>
+        <v>3206.05</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>633.84</v>
+        <v>641.21</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P133" t="inlineStr"/>
@@ -16630,17 +16630,17 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=19-CP-002176</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038515</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 19-CP-002176</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-038515</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16688,12 +16688,12 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>24-CC-071254</t>
+          <t>19-CP-002176</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Naidu, Konisj</t>
+          <t>LARA, PABLO A</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>3161.5</v>
+        <v>3169.22</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>632.3</v>
+        <v>633.84</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -16752,17 +16752,17 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CC-071254</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-002176</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-071254</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 19-CP-002176</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -16787,12 +16787,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16810,12 +16810,12 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>25-CC-005974</t>
+          <t>24-CC-071254</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>EASON, CHRISTINE</t>
+          <t>Naidu, Konisj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -16840,7 +16840,7 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>3132</v>
+        <v>3161.5</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>626.4</v>
+        <v>632.3</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P135" t="inlineStr"/>
@@ -16874,17 +16874,17 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-005974</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-071254</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CC-005974</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-071254</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
@@ -16909,12 +16909,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16932,12 +16932,12 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>26-CC-021342</t>
+          <t>25-CC-005974</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>DAWSON, SHANSHE</t>
+          <t>EASON, CHRISTINE</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -16962,7 +16962,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>3000</v>
+        <v>3132</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>600</v>
+        <v>626.4</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P136" t="inlineStr"/>
@@ -16996,17 +16996,17 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-021342</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-005974</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-021342</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CC-005974</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
@@ -17031,12 +17031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17054,12 +17054,12 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>26-CC-041752</t>
+          <t>26-CC-021342</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SHELLINGS, CORIEANNA</t>
+          <t>DAWSON, SHANSHE</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -17084,7 +17084,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>2959.69</v>
+        <v>3000</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         </is>
       </c>
       <c r="M137" t="n">
-        <v>591.9400000000001</v>
+        <v>600</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -17118,17 +17118,17 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-041752</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-021342</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-041752</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-021342</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
@@ -17153,12 +17153,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17176,12 +17176,12 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>26-CC-048322</t>
+          <t>26-CC-041752</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mateo, Francis</t>
+          <t>SHELLINGS, CORIEANNA</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -17206,7 +17206,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>2947.5</v>
+        <v>2959.69</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>589.5</v>
+        <v>591.9400000000001</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -17240,17 +17240,17 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-048322</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041752</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-048322</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-041752</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17298,12 +17298,12 @@
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>26-CC-039167</t>
+          <t>26-CC-048322</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dekhtyar, Gennady</t>
+          <t>Mateo, Francis</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>2913.5</v>
+        <v>2947.5</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         </is>
       </c>
       <c r="M139" t="n">
-        <v>582.7</v>
+        <v>589.5</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -17362,17 +17362,17 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-039167</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048322</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-039167</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-048322</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17420,12 +17420,12 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>26-CC-042274</t>
+          <t>26-CC-039167</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Gearin, Heather</t>
+          <t>Dekhtyar, Gennady</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -17450,7 +17450,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>2905</v>
+        <v>2913.5</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         </is>
       </c>
       <c r="M140" t="n">
-        <v>581</v>
+        <v>582.7</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P140" t="inlineStr"/>
@@ -17484,17 +17484,17 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-042274</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-039167</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-042274</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-039167</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -17519,12 +17519,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17542,12 +17542,12 @@
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>22-CA-007538</t>
+          <t>26-CC-042274</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Holcomb, Christopher</t>
+          <t>Gearin, Heather</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -17606,17 +17606,17 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042274</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-007538</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-042274</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
@@ -17641,12 +17641,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17664,12 +17664,12 @@
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>25-CC-053184</t>
+          <t>22-CA-007538</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>DURAN, LUIS</t>
+          <t>Holcomb, Christopher</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -17694,7 +17694,7 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>2888.69</v>
+        <v>2905</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>577.74</v>
+        <v>581</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
@@ -17728,17 +17728,17 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CC-053184</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CC-053184</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-007538</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17786,12 +17786,12 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>11-CC-033178</t>
+          <t>25-CC-053184</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ALI, AHMAD</t>
+          <t>DURAN, LUIS</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>2863.77</v>
+        <v>2888.69</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="M143" t="n">
-        <v>572.75</v>
+        <v>577.74</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
@@ -17850,17 +17850,17 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=11-CC-033178</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-053184</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 11-CC-033178</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CC-053184</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
@@ -17885,12 +17885,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17908,12 +17908,12 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>26-CC-037076</t>
+          <t>11-CC-033178</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CARDENAS, ALYSSA</t>
+          <t>ALI, AHMAD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>2837.99</v>
+        <v>2863.77</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         </is>
       </c>
       <c r="M144" t="n">
-        <v>567.6</v>
+        <v>572.75</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
@@ -17972,17 +17972,17 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-037076</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=11-CC-033178</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-037076</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 11-CC-033178</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18030,12 +18030,12 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>26-CC-039160</t>
+          <t>26-CC-037076</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Williams, Robert</t>
+          <t>CARDENAS, ALYSSA</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -18060,7 +18060,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>2818.2</v>
+        <v>2837.99</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>563.64</v>
+        <v>567.6</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -18094,17 +18094,17 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-039160</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-037076</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-039160</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-037076</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
@@ -18129,12 +18129,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18152,12 +18152,12 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>26-CC-037636</t>
+          <t>26-CC-039160</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hough, Romarick</t>
+          <t>Williams, Robert</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -18182,7 +18182,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>2799.75</v>
+        <v>2818.2</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
       <c r="M146" t="n">
-        <v>559.95</v>
+        <v>563.64</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P146" t="inlineStr"/>
@@ -18216,17 +18216,17 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-037636</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-039160</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-037636</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-039160</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -18251,12 +18251,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18274,12 +18274,12 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>04-CP-001992</t>
+          <t>26-CC-037636</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>NUNEZ, JUANA</t>
+          <t>Hough, Romarick</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>2797.22</v>
+        <v>2799.75</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         </is>
       </c>
       <c r="M147" t="n">
-        <v>559.4400000000001</v>
+        <v>559.95</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -18338,17 +18338,17 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=04-CP-001992</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-037636</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 04-CP-001992</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-037636</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -18373,12 +18373,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18396,12 +18396,12 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>22-CC-055454</t>
+          <t>04-CP-001992</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rodriguez, Alberto</t>
+          <t>NUNEZ, JUANA</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -18426,7 +18426,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>2795.2</v>
+        <v>2797.22</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         </is>
       </c>
       <c r="M148" t="n">
-        <v>559.04</v>
+        <v>559.4400000000001</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
@@ -18460,17 +18460,17 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=22-CC-055454</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=04-CP-001992</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CC-055454</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 04-CP-001992</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>24-CC-027384</t>
+          <t>22-CC-055454</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>MIRAZOVAC, LASZLO PEK</t>
+          <t>Rodriguez, Alberto</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -18548,7 +18548,7 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>2750.5</v>
+        <v>2795.2</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         </is>
       </c>
       <c r="M149" t="n">
-        <v>550.1</v>
+        <v>559.04</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -18582,17 +18582,17 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CC-027384</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CC-055454</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-027384</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CC-055454</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -18617,12 +18617,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18640,12 +18640,12 @@
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>24-CC-004190</t>
+          <t>24-CC-027384</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>BARBER, WENDY LEE</t>
+          <t>MIRAZOVAC, LASZLO PEK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>2748</v>
+        <v>2750.5</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         </is>
       </c>
       <c r="M150" t="n">
-        <v>549.6</v>
+        <v>550.1</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P150" t="inlineStr"/>
@@ -18704,17 +18704,17 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CC-004190</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-027384</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-004190</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-027384</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18762,12 +18762,12 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>26-CC-009598</t>
+          <t>24-CC-004190</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PARKER, PRISCILLA</t>
+          <t>BARBER, WENDY LEE</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -18792,7 +18792,7 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>2699</v>
+        <v>2748</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         </is>
       </c>
       <c r="M151" t="n">
-        <v>539.8</v>
+        <v>549.6</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P151" t="inlineStr"/>
@@ -18826,17 +18826,17 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-009598</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-004190</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-009598</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-004190</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -18861,12 +18861,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18884,12 +18884,12 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>26-LW-000450</t>
+          <t>26-CC-009598</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000450)</t>
+          <t>PARKER, PRISCILLA</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -18905,16 +18905,16 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="K152" t="n">
-        <v>2652.06</v>
+        <v>2699</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         </is>
       </c>
       <c r="M152" t="n">
-        <v>530.41</v>
+        <v>539.8</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
@@ -18943,52 +18943,52 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-009598</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000450</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-009598</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19006,12 +19006,12 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>26-CC-048666</t>
+          <t>26-LW-000450</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FORD, ASHANTI J.</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000450)</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -19027,16 +19027,16 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
+          <t>Vacant Land / Acreage</t>
         </is>
       </c>
       <c r="K153" t="n">
-        <v>2644</v>
+        <v>2652.06</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         </is>
       </c>
       <c r="M153" t="n">
-        <v>528.8</v>
+        <v>530.41</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -19065,52 +19065,52 @@
       <c r="R153" t="inlineStr"/>
       <c r="S153" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-048666</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-048666</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000450</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19128,12 +19128,12 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>26-CC-041645</t>
+          <t>26-CC-048666</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>BAUMGARDNER, LETTIE</t>
+          <t>FORD, ASHANTI J.</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -19158,7 +19158,7 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>2631.34</v>
+        <v>2644</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>526.27</v>
+        <v>528.8</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -19192,17 +19192,17 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-041645</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048666</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-041645</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-048666</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -19227,12 +19227,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19250,12 +19250,12 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>26-CC-047526</t>
+          <t>26-CC-041645</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Davis, India</t>
+          <t>BAUMGARDNER, LETTIE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -19280,7 +19280,7 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>2592.56</v>
+        <v>2631.34</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         </is>
       </c>
       <c r="M155" t="n">
-        <v>518.51</v>
+        <v>526.27</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
@@ -19314,17 +19314,17 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-047526</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041645</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-047526</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-041645</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19372,12 +19372,12 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>24-CC-067400</t>
+          <t>26-CC-047526</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>BUCKLEY, ROGER</t>
+          <t>Davis, India</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -19402,7 +19402,7 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>2578.43</v>
+        <v>2592.56</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         </is>
       </c>
       <c r="M156" t="n">
-        <v>515.6900000000001</v>
+        <v>518.51</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
@@ -19436,17 +19436,17 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=24-CC-067400</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047526</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-067400</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-047526</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
@@ -19471,12 +19471,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19494,12 +19494,12 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>25-CA-005347</t>
+          <t>24-CC-067400</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Kennedy, Willa Helen</t>
+          <t>BUCKLEY, ROGER</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -19524,7 +19524,7 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>2546</v>
+        <v>2578.43</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="M157" t="n">
-        <v>509.2</v>
+        <v>515.6900000000001</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -19558,17 +19558,17 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-067400</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-005347</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CC-067400</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -19593,12 +19593,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-19T13:10:34Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-19 13:10:46</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19616,12 +19616,12 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>26-CC-047535</t>
+          <t>26-CC-047346</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Harwell, Adina</t>
+          <t>SHOULDERS, RODNEY</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -19646,7 +19646,7 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>2528</v>
+        <v>2553.5</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         </is>
       </c>
       <c r="M158" t="n">
-        <v>505.6</v>
+        <v>510.7</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
@@ -19680,47 +19680,291 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf#search=26-CC-047535</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047346</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
         <is>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-047346</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-10-20T11:33:36Z</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:33:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>25-CA-005347</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Kennedy, Willa Helen</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G159" t="b">
+        <v>1</v>
+      </c>
+      <c r="H159" t="b">
+        <v>0</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>2546</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>509.2</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Confirm window with clerk</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CA-005347</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-005347</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-10-20T11:33:36Z</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:33:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>26-CC-047535</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Harwell, Adina</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G160" t="b">
+        <v>1</v>
+      </c>
+      <c r="H160" t="b">
+        <v>0</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>2528</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>505.6</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Confirm window with clerk</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047535</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
           <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CC-047535</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_16_2026.pdf</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 45.032</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 45.032</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
         <is>
           <t>Foreclosure Surplus</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
+      <c r="Z160" t="inlineStr">
         <is>
           <t>FORECLOSURE</t>
         </is>
       </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>2026-10-19T13:10:34Z</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>2026-10-19 13:10:46</t>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-10-20T11:33:36Z</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-008975</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CA-008975</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-002386</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-002386</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-002619</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-002619</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-002515</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-002515</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-000212</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CP-000212</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=15-CA-001463</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=15-CA-001463</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-002439</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CP-002439</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=14-CC-036459</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=14-CC-036459</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-004050</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CP-004050</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-011013</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-011013</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-002815</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CP-002815</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-000093</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=19-CP-000093</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-001816</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-001816</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-002495</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CP-002495</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-053397</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-053397</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=17-CA-001731</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=17-CA-001731</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-000236</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-000236</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=15-CP-001594</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=15-CP-001594</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-025679</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-025679</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-000331</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=19-CP-000331</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-008539</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-008539</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CC-012552</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CC-012552</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=14-CP-001685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=14-CP-001685</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9223,12 +9223,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-040872</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-040872</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -9467,12 +9467,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=89-CP-000329</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=89-CP-000329</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=18-CP-000981</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=18-CP-000981</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9711,12 +9711,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=13-CP-000149</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=13-CP-000149</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-001829</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-001829</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CC-090753</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CC-090753</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033697</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033697</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-044373</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-044373</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-021712</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-021712</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033927</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033927</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038836</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-038836</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -10687,12 +10687,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-004204</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-004204</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P88" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042698</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042698</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-030765</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-030765</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036800</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-036800</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-046797</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-046797</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036196</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-036196</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-002379</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-002379</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047045</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047045</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12151,12 +12151,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-031087</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-031087</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041455</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-041455</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -12395,12 +12395,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -12517,12 +12517,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-003171</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-003171</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-022913</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-022913</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-057250</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-057250</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-003139</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-003139</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -13127,12 +13127,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-040382</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-040382</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033877</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033877</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036763</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-036763</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -13493,12 +13493,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P108" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-018307</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-018307</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P109" t="inlineStr"/>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-045915</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-045915</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P110" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-015407</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-015407</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -13859,12 +13859,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-028992</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-028992</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P112" t="inlineStr"/>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-045789</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-045789</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -14103,12 +14103,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P113" t="inlineStr"/>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-054158</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-054158</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -14225,12 +14225,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P114" t="inlineStr"/>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-008441</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-008441</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P115" t="inlineStr"/>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048032</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048032</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P116" t="inlineStr"/>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-001543</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CP-001543</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14661,7 +14661,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-025860</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-025860</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P118" t="inlineStr"/>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-020536</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-020536</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -14835,12 +14835,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
@@ -14922,7 +14922,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042880</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042880</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P120" t="inlineStr"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033916</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033916</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -15079,12 +15079,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-066151</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-066151</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P122" t="inlineStr"/>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038737</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-038737</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -15323,12 +15323,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P123" t="inlineStr"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046372</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046372</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P124" t="inlineStr"/>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048087</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048087</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -15567,12 +15567,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048006</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048006</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P126" t="inlineStr"/>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046665</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046665</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
@@ -15811,12 +15811,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-011115</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-011115</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -15933,12 +15933,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046414</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046414</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
@@ -16055,12 +16055,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P129" t="inlineStr"/>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042617</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042617</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P130" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-040526</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-040526</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P131" t="inlineStr"/>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-002624</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-002624</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
@@ -16421,12 +16421,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P132" t="inlineStr"/>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046381</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046381</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
@@ -16543,12 +16543,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P133" t="inlineStr"/>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038515</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-038515</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-002176</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=19-CP-002176</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -16787,12 +16787,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P135" t="inlineStr"/>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-071254</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-071254</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
@@ -16909,12 +16909,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P136" t="inlineStr"/>
@@ -16996,7 +16996,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-005974</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-005974</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
@@ -17031,12 +17031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-021342</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-021342</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
@@ -17153,12 +17153,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041752</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-041752</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048322</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048322</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -17372,7 +17372,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17467,7 +17467,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P140" t="inlineStr"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-039167</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-039167</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -17519,12 +17519,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042274</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042274</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
@@ -17641,12 +17641,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-053184</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-053184</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
@@ -17885,12 +17885,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17955,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=11-CC-033178</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=11-CC-033178</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-037076</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-037076</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
@@ -18129,12 +18129,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P146" t="inlineStr"/>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-039160</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-039160</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -18251,12 +18251,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-037636</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-037636</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -18373,12 +18373,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
@@ -18460,7 +18460,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=04-CP-001992</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=04-CP-001992</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -18582,7 +18582,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CC-055454</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CC-055454</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -18617,12 +18617,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P150" t="inlineStr"/>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-027384</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-027384</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P151" t="inlineStr"/>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-004190</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-004190</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -18861,12 +18861,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -18931,7 +18931,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-009598</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-009598</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -18983,12 +18983,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19105,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:35Z</t>
+          <t>2026-10-21T11:46:14Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048666</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048666</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -19227,12 +19227,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041645</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-041645</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -19324,7 +19324,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047526</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047526</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
@@ -19471,12 +19471,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-067400</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-067400</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -19593,12 +19593,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047346</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047346</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
@@ -19715,12 +19715,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P159" t="inlineStr"/>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047535</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047535</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
@@ -19959,12 +19959,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-20T11:33:36Z</t>
+          <t>2026-10-21T11:46:15Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-20 11:33:46</t>
+          <t>2026-10-21 11:46:25</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CA-008975</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-008975</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-002386</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-002386</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-002619</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-002619</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-002515</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-002515</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CP-000212</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-000212</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=15-CA-001463</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=15-CA-001463</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CP-002439</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-002439</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=14-CC-036459</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=14-CC-036459</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CP-004050</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CP-004050</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-011013</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-011013</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CP-002815</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-002815</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=19-CP-000093</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-000093</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-001816</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-001816</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CP-002495</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-002495</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-053397</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-053397</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=17-CA-001731</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=17-CA-001731</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-000236</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-000236</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=15-CP-001594</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=15-CP-001594</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-025679</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-025679</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=19-CP-000331</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-000331</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-008539</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-008539</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CC-012552</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CC-012552</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=14-CP-001685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=14-CP-001685</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P71" t="inlineStr"/>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P72" t="inlineStr"/>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -9223,12 +9223,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9345,12 +9345,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P74" t="inlineStr"/>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-040872</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-040872</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -9467,12 +9467,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P75" t="inlineStr"/>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=89-CP-000329</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=89-CP-000329</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=18-CP-000981</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=18-CP-000981</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -9711,12 +9711,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=13-CP-000149</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=13-CP-000149</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P78" t="inlineStr"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-001829</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-001829</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CC-090753</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CC-090753</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033697</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033697</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
@@ -10199,12 +10199,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-044373</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-044373</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P82" t="inlineStr"/>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-021712</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-021712</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033927</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033927</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-038836</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038836</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -10687,12 +10687,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P86" t="inlineStr"/>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W86" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P87" t="inlineStr"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-004204</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-004204</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P88" t="inlineStr"/>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042698</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042698</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P89" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-030765</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-030765</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P90" t="inlineStr"/>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-036800</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036800</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P91" t="inlineStr"/>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-046797</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-046797</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W91" t="inlineStr">
@@ -11541,12 +11541,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P92" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-036196</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036196</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-002379</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-002379</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W94" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047045</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047045</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
@@ -12029,12 +12029,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12151,12 +12151,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P97" t="inlineStr"/>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-031087</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-031087</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12273,12 +12273,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-041455</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041455</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W98" t="inlineStr">
@@ -12395,12 +12395,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -12517,12 +12517,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P100" t="inlineStr"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CP-003171</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CP-003171</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-022913</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-022913</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-057250</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-057250</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-003139</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-003139</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -13127,12 +13127,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-040382</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-040382</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13319,7 +13319,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P106" t="inlineStr"/>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033877</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033877</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P107" t="inlineStr"/>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-036763</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-036763</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -13493,12 +13493,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P108" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-018307</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-018307</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P109" t="inlineStr"/>
@@ -13702,7 +13702,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-045915</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-045915</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P110" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-015407</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-015407</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -13859,12 +13859,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P111" t="inlineStr"/>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-028992</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-028992</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P112" t="inlineStr"/>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-045789</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-045789</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -14103,12 +14103,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14173,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P113" t="inlineStr"/>
@@ -14190,7 +14190,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-054158</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-054158</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -14225,12 +14225,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P114" t="inlineStr"/>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-008441</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-008441</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P115" t="inlineStr"/>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048032</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048032</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P116" t="inlineStr"/>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CP-001543</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CP-001543</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -14591,12 +14591,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14661,7 +14661,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P117" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-025860</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-025860</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P118" t="inlineStr"/>
@@ -14800,7 +14800,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-020536</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-020536</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -14810,7 +14810,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -14835,12 +14835,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -14905,7 +14905,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P119" t="inlineStr"/>
@@ -14922,7 +14922,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042880</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042880</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -14957,12 +14957,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15027,7 +15027,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P120" t="inlineStr"/>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-033916</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-033916</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -15079,12 +15079,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-066151</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-066151</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P122" t="inlineStr"/>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-038737</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038737</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -15323,12 +15323,12 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P123" t="inlineStr"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046372</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046372</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
@@ -15445,12 +15445,12 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P124" t="inlineStr"/>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048087</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048087</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
@@ -15567,12 +15567,12 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048006</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048006</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P126" t="inlineStr"/>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046665</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046665</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
@@ -15811,12 +15811,12 @@
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P127" t="inlineStr"/>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-011115</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-011115</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
@@ -15933,12 +15933,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16003,7 +16003,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046414</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046414</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
@@ -16055,12 +16055,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P129" t="inlineStr"/>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042617</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042617</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
@@ -16177,12 +16177,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P130" t="inlineStr"/>
@@ -16264,7 +16264,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-040526</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-040526</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="V130" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W130" t="inlineStr">
@@ -16299,12 +16299,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P131" t="inlineStr"/>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=23-CP-002624</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=23-CP-002624</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
@@ -16421,12 +16421,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P132" t="inlineStr"/>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-046381</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-046381</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
@@ -16543,12 +16543,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P133" t="inlineStr"/>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-038515</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-038515</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
@@ -16665,12 +16665,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=19-CP-002176</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=19-CP-002176</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="V134" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W134" t="inlineStr">
@@ -16787,12 +16787,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P135" t="inlineStr"/>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-071254</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-071254</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
@@ -16909,12 +16909,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P136" t="inlineStr"/>
@@ -16996,7 +16996,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-005974</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-005974</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
@@ -17031,12 +17031,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-021342</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-021342</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
@@ -17153,12 +17153,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P138" t="inlineStr"/>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-041752</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041752</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048322</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048322</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -17372,7 +17372,7 @@
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
@@ -17397,12 +17397,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17467,7 +17467,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P140" t="inlineStr"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-039167</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-039167</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
@@ -17519,12 +17519,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-042274</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-042274</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
@@ -17641,12 +17641,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -17763,12 +17763,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CC-053184</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CC-053184</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
@@ -17885,12 +17885,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17955,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
@@ -17972,7 +17972,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=11-CC-033178</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=11-CC-033178</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18077,7 +18077,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-037076</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-037076</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
@@ -18129,12 +18129,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P146" t="inlineStr"/>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-039160</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-039160</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
@@ -18251,12 +18251,12 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-037636</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-037636</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -18373,12 +18373,12 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
@@ -18460,7 +18460,7 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=04-CP-001992</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=04-CP-001992</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="V148" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18565,7 +18565,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -18582,7 +18582,7 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=22-CC-055454</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=22-CC-055454</t>
         </is>
       </c>
       <c r="U149" t="inlineStr">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -18617,12 +18617,12 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P150" t="inlineStr"/>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-027384</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-027384</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P151" t="inlineStr"/>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-004190</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-004190</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
@@ -18861,12 +18861,12 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -18931,7 +18931,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
@@ -18948,7 +18948,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-009598</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-009598</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
@@ -18983,12 +18983,12 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19105,12 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:14Z</t>
+          <t>2026-10-20T11:33:35Z</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-048666</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-048666</t>
         </is>
       </c>
       <c r="U154" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
@@ -19227,12 +19227,12 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
@@ -19314,7 +19314,7 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-041645</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-041645</t>
         </is>
       </c>
       <c r="U155" t="inlineStr">
@@ -19324,7 +19324,7 @@
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -19349,12 +19349,12 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047526</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047526</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
@@ -19471,12 +19471,12 @@
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=24-CC-067400</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=24-CC-067400</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
@@ -19593,12 +19593,12 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047346</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047346</t>
         </is>
       </c>
       <c r="U158" t="inlineStr">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
@@ -19715,12 +19715,12 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P159" t="inlineStr"/>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U159" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>
@@ -19907,7 +19907,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf#search=26-CC-047535</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf#search=26-CC-047535</t>
         </is>
       </c>
       <c r="U160" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="V160" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_20_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_19_2026.pdf</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
@@ -19959,12 +19959,12 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2026-10-21T11:46:15Z</t>
+          <t>2026-10-20T11:33:36Z</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-21 11:46:25</t>
+          <t>2026-10-20 11:33:46</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:37Z</t>
+          <t>2026-10-23T09:18:50Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_21_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-22T09:22:38Z</t>
+          <t>2026-10-23T09:18:51Z</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-22 09:22:48</t>
+          <t>2026-10-23 09:19:05</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB60"/>
+  <dimension ref="A1:AB59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2536,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>26-LW-000003</t>
+          <t>16-LW-000319</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000003)</t>
+          <t>Tax Deed Titleholder of Record (File 16-LW-000319)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>60466.87</v>
+        <v>59530.89</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>12093.37</v>
+        <v>11906.18</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000003</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 16-LW-000319</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16-LW-000319</t>
+          <t>25-LW-000326</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 16-LW-000319)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000326)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>59530.89</v>
+        <v>59247.79</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>11906.18</v>
+        <v>11849.56</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 16-LW-000319</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000326</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25-LW-000326</t>
+          <t>26-LW-000457</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000326)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000457)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>59247.79</v>
+        <v>51045.53</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>11849.56</v>
+        <v>10209.11</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000326</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000457</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26-LW-000457</t>
+          <t>26-LW-000119</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000457)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000119)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>51045.53</v>
+        <v>49644.45</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>10209.11</v>
+        <v>9928.889999999999</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000457</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000119</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>26-LW-000119</t>
+          <t>25-LW-000429</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000119)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000429)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>49644.45</v>
+        <v>47357.27</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>9928.889999999999</v>
+        <v>9471.450000000001</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000119</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000429</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>25-LW-000429</t>
+          <t>26-LW-000065</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000429)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000065)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>47357.27</v>
+        <v>47251.64</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>9471.450000000001</v>
+        <v>9450.33</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000429</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000065</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3268,12 +3268,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26-LW-000065</t>
+          <t>23-CA-017541</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000065)</t>
+          <t>Riffey, Carolyn E</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>47251.64</v>
+        <v>42527.06</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>9450.33</v>
+        <v>8505.41</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3327,52 +3327,52 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000065</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-017541</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23-CA-017541</t>
+          <t>21-CA-005559</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Riffey, Carolyn E</t>
+          <t>LOMOGLIO, KAREN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>42527.06</v>
+        <v>39392.5</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>8505.41</v>
+        <v>7878.5</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3454,17 +3454,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-017541</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-005559</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3512,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21-CA-005559</t>
+          <t>26-LW-000468</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LOMOGLIO, KAREN</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000468)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>39392.5</v>
+        <v>34957.15</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>7878.5</v>
+        <v>6991.43</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3571,52 +3571,52 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=21-CA-005559</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-005559</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000468</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3634,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26-LW-000468</t>
+          <t>26-LW-000147</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000468)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000147)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>34957.15</v>
+        <v>34484.85</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>6991.43</v>
+        <v>6896.97</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000468</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000147</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26-LW-000147</t>
+          <t>21-LW-000522</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000147)</t>
+          <t>Tax Deed Titleholder of Record (File 21-LW-000522)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>34484.85</v>
+        <v>34125.04</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>6896.97</v>
+        <v>6825.01</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000147</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 21-LW-000522</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3878,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21-LW-000522</t>
+          <t>26-LW-000447</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 21-LW-000522)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000447)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>34125.04</v>
+        <v>30869.06</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>6825.01</v>
+        <v>6173.81</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 21-LW-000522</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000447</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4000,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26-LW-000447</t>
+          <t>22-LW-000082</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000447)</t>
+          <t>Tax Deed Titleholder of Record (File 22-LW-000082)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>30869.06</v>
+        <v>30182.05</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>6173.81</v>
+        <v>6036.41</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000447</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 22-LW-000082</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22-LW-000082</t>
+          <t>21-CA-004936</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 22-LW-000082)</t>
+          <t>Vega, Luis Orlando</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>30182.05</v>
+        <v>29749.43</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>6036.41</v>
+        <v>5949.89</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4181,52 +4181,52 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 22-LW-000082</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-004936</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21-CA-004936</t>
+          <t>23-LW-001012</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vega, Luis Orlando</t>
+          <t>Tax Deed Titleholder of Record (File 23-LW-001012)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>29749.43</v>
+        <v>29678.67</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5949.89</v>
+        <v>5935.73</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -4303,52 +4303,52 @@
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=21-CA-004936</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-004936</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 23-LW-001012</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23-LW-001012</t>
+          <t>23-CA-014882</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 23-LW-001012)</t>
+          <t>Reid, Morris Anthony</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>29678.67</v>
+        <v>24750</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4404,16 +4404,16 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>5935.73</v>
+        <v>4950</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Tier 1: High Value ($25k+)</t>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4425,52 +4425,52 @@
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 23-LW-001012</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-014882</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23-CA-014882</t>
+          <t>26-LW-000585</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reid, Morris Anthony</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000585)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>24750</v>
+        <v>23777.45</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4950</v>
+        <v>4755.49</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4547,52 +4547,52 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-014882</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-014882</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000585</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4610,12 +4610,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>25-LW-000378</t>
+          <t>25-LW-000404</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000378)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000404)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>23874.09</v>
+        <v>22389.16</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4774.82</v>
+        <v>4477.83</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000378</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000404</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4732,12 +4732,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26-LW-000585</t>
+          <t>26-LW-000462</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000585)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000462)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>23777.45</v>
+        <v>21981.08</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>4755.49</v>
+        <v>4396.22</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000585</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000462</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>25-LW-000404</t>
+          <t>26-LW-000702</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000404)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000702)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>22389.16</v>
+        <v>20975.22</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4477.83</v>
+        <v>4195.04</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000404</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000702</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -4976,12 +4976,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26-LW-000462</t>
+          <t>26-LW-000443</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000462)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000443)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>21981.08</v>
+        <v>19884.83</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4396.22</v>
+        <v>3976.97</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000462</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000443</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26-LW-000443</t>
+          <t>26-CA-000549</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000443)</t>
+          <t>ARRIOLA, CINDY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>19884.83</v>
+        <v>19279.69</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>3976.97</v>
+        <v>3855.94</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -5157,52 +5157,52 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000443</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-000549</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5220,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26-CA-000549</t>
+          <t>26-LW-000487</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ARRIOLA, CINDY</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000487)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>19279.69</v>
+        <v>18986.52</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>3855.94</v>
+        <v>3797.3</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -5279,52 +5279,52 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=26-CA-000549</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-000549</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000487</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5342,12 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>26-LW-000487</t>
+          <t>25-CA-002135</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000487)</t>
+          <t>Chandler, Matthew B</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>18986.52</v>
+        <v>14603.48</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>3797.3</v>
+        <v>2920.7</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5401,52 +5401,52 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000487</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-002135</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5464,12 +5464,12 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>25-CA-002135</t>
+          <t>22-CA-008602</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chandler, Matthew B</t>
+          <t>PORTO , CURRAN KIM</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>14603.48</v>
+        <v>14460.18</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>2920.7</v>
+        <v>2892.04</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -5528,17 +5528,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-002135</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-008602</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5586,12 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22-CA-008602</t>
+          <t>25-LW-000342</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PORTO , CURRAN KIM</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000342)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>14460.18</v>
+        <v>13694.79</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>2892.04</v>
+        <v>2738.96</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -5645,52 +5645,52 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=22-CA-008602</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-008602</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000342</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5708,12 +5708,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>25-LW-000342</t>
+          <t>25-LW-000397</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000342)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000397)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>13694.79</v>
+        <v>12322.8</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2738.96</v>
+        <v>2464.56</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000342</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000397</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>25-LW-000397</t>
+          <t>25-LW-000531</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000397)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000531)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>12322.8</v>
+        <v>11561.97</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>2464.56</v>
+        <v>2312.39</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000397</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000531</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>25-LW-000531</t>
+          <t>25-LW-000252</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000531)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000252)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>11561.97</v>
+        <v>10573.8</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>2312.39</v>
+        <v>2114.76</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000531</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000252</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>25-LW-000252</t>
+          <t>26-CA-007844</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000252)</t>
+          <t>KOLINSKI, KEVIN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>10573.8</v>
+        <v>10500</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>2114.76</v>
+        <v>2100</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -6133,52 +6133,52 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000252</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-007844</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6196,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>26-CA-007844</t>
+          <t>18-CA-007512</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KOLINSKI, KEVIN</t>
+          <t>Kinkoff, Richard R</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>10500</v>
+        <v>10000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -6260,17 +6260,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-007844</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 18-CA-007512</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6318,12 +6318,12 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>18-CA-007512</t>
+          <t>25-LW-000118</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kinkoff, Richard R</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000118)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>10000</v>
+        <v>9921.51</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -6356,16 +6356,16 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>2000</v>
+        <v>1984.3</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tier 2: Medium Value ($10k-$25k)</t>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -6377,52 +6377,52 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=18-CA-007512</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 18-CA-007512</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000118</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>25-LW-000118</t>
+          <t>25-LW-000549</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000118)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000549)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>9921.51</v>
+        <v>7627.26</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1984.3</v>
+        <v>1525.45</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000118</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000549</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6562,12 +6562,12 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>25-LW-000549</t>
+          <t>09-CA-009881</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000549)</t>
+          <t>MULLIS, LISA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>7627.26</v>
+        <v>7402.89</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1525.45</v>
+        <v>1480.58</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6621,52 +6621,52 @@
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000549</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 09-CA-009881</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>09-CA-009881</t>
+          <t>24-CA-000685</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MULLIS, LISA</t>
+          <t>ERCHID , OMAR A</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>7402.89</v>
+        <v>6447.5</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1480.58</v>
+        <v>1289.5</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,17 +6748,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 09-CA-009881</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-000685</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>24-CA-000685</t>
+          <t>25-LW-000564</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ERCHID , OMAR A</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000564)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>6447.5</v>
+        <v>5944.21</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>1289.5</v>
+        <v>1188.84</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -6865,52 +6865,52 @@
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=24-CA-000685</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-000685</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000564</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -6928,12 +6928,12 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>25-LW-000564</t>
+          <t>24-CA-005012</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000564)</t>
+          <t>MURILLO, ANGELA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>5944.21</v>
+        <v>5681.72</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1188.84</v>
+        <v>1136.34</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6987,52 +6987,52 @@
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000564</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-005012</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>24-CA-005012</t>
+          <t>26-LW-000404</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MURILLO, ANGELA</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000404)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>5681.72</v>
+        <v>5223.53</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1136.34</v>
+        <v>1044.71</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -7109,52 +7109,52 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=24-CA-005012</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-005012</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000404</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7172,12 +7172,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>26-LW-000404</t>
+          <t>23-CA-000671</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000404)</t>
+          <t>DENNIS HERNANDEZ &amp; ASSOCIATES, P.A</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>5223.53</v>
+        <v>3807.59</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1044.71</v>
+        <v>761.52</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7231,52 +7231,52 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000404</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-000671</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7294,12 +7294,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23-CA-000671</t>
+          <t>22-CA-007538</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DENNIS HERNANDEZ &amp; ASSOCIATES, P.A</t>
+          <t>Holcomb, Christopher</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>3807.59</v>
+        <v>2905</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>761.52</v>
+        <v>581</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,17 +7358,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-000671</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-007538</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7416,12 +7416,12 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22-CA-007538</t>
+          <t>26-LW-000450</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Holcomb, Christopher</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000450)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>2905</v>
+        <v>2652.06</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>581</v>
+        <v>530.41</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -7475,52 +7475,52 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=22-CA-007538</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-007538</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000450</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:51Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7538,12 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>26-LW-000450</t>
+          <t>25-CA-005347</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000450)</t>
+          <t>Kennedy, Willa Helen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>2652.06</v>
+        <v>2546</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>530.41</v>
+        <v>509.2</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -7597,174 +7597,52 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000450</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-005347</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-23T09:18:50Z</t>
+          <t>2026-10-24T08:50:32Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-23 09:19:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Hillsborough</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>25-CA-005347</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Kennedy, Willa Helen</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>2546</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="M60" t="n">
-        <v>509.2</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Confirm window with clerk</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf#search=25-CA-005347</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-005347</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_22_2026.pdf</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 45.032</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 45.032</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Foreclosure Surplus</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>FORECLOSURE</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-10-23T09:18:51Z</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:19:05</t>
+          <t>2026-10-24 08:50:41</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:14Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-24T08:50:32Z</t>
+          <t>2026-10-25T09:07:15Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-24 08:50:41</t>
+          <t>2026-10-25 09:07:27</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:14Z</t>
+          <t>2026-10-26T10:03:05Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-25T09:07:15Z</t>
+          <t>2026-10-26T10:03:06Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-25 09:07:27</t>
+          <t>2026-10-26 10:03:18</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:05Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_23_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-26T10:03:06Z</t>
+          <t>2026-10-27T09:47:06Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-26 10:03:18</t>
+          <t>2026-10-27 09:47:17</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:02Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Mon_10_26_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-27T09:47:06Z</t>
+          <t>2026-10-28T10:32:03Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-27 09:47:17</t>
+          <t>2026-10-28 10:32:15</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:02Z</t>
+          <t>2026-10-29T10:51:31Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Tue_10_27_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-28T10:32:03Z</t>
+          <t>2026-10-29T10:51:32Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-28 10:32:15</t>
+          <t>2026-10-29 10:51:45</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=24-CA-001841</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-017541</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=21-CA-004936</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4831,12 +4831,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=26-CA-000549</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=25-CA-002135</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=26-CA-007844</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=18-CA-007512</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6539,12 +6539,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=24-CA-000685</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=23-CA-000671</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=22-CA-007538</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:31Z</t>
+          <t>2026-10-30T10:50:33Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=25-CA-005347</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Wed_10_28_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-29T10:51:32Z</t>
+          <t>2026-10-30T10:50:35Z</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-29 10:51:45</t>
+          <t>2026-10-30 10:50:47</t>
         </is>
       </c>
     </row>

--- a/exports/Florida_Surplus_Feed.xlsx
+++ b/exports/Florida_Surplus_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB59"/>
+  <dimension ref="A1:AB62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -631,7 +631,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -683,12 +683,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -805,12 +805,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-016325</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=23-CA-016325</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=26-CA-006185</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=26-CA-006185</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1926,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24-CA-001841</t>
+          <t>26-LW-000721</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CHINNERY, PATRICE</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000721)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>75684.39999999999</v>
+        <v>79630.21000000001</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>15136.88</v>
+        <v>15926.04</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1985,52 +1985,52 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=24-CA-001841</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-001841</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000721</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26-LW-000314</t>
+          <t>24-CA-001841</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000314)</t>
+          <t>CHINNERY, PATRICE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>71541.7</v>
+        <v>75684.39999999999</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>14308.34</v>
+        <v>15136.88</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -2107,52 +2107,52 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=24-CA-001841</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000314</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-001841</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2170,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26-LW-000398</t>
+          <t>26-LW-000314</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000398)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000314)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>65374.21</v>
+        <v>71541.7</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>13074.84</v>
+        <v>14308.34</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000398</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000314</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2292,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26-LW-000532</t>
+          <t>26-LW-000398</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000532)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000398)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>64868.17</v>
+        <v>65374.21</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>12973.63</v>
+        <v>13074.84</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000532</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000398</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26-LW-000488</t>
+          <t>26-LW-000532</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000488)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000532)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>61189.91</v>
+        <v>64868.17</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>12237.98</v>
+        <v>12973.63</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000488</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000532</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2536,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16-LW-000319</t>
+          <t>26-LW-000488</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 16-LW-000319)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000488)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>59530.89</v>
+        <v>61189.91</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>11906.18</v>
+        <v>12237.98</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 16-LW-000319</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000488</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2658,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25-LW-000326</t>
+          <t>16-LW-000319</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000326)</t>
+          <t>Tax Deed Titleholder of Record (File 16-LW-000319)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2688,7 +2688,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>59247.79</v>
+        <v>59530.89</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>11849.56</v>
+        <v>11906.18</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000326</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 16-LW-000319</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>26-LW-000457</t>
+          <t>25-LW-000326</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000457)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000326)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>51045.53</v>
+        <v>59247.79</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>10209.11</v>
+        <v>11849.56</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000457</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000326</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26-LW-000119</t>
+          <t>26-LW-000457</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000119)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000457)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>49644.45</v>
+        <v>51045.53</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>9928.889999999999</v>
+        <v>10209.11</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000119</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000457</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25-LW-000429</t>
+          <t>26-LW-000119</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000429)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000119)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>47357.27</v>
+        <v>49644.45</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>9471.450000000001</v>
+        <v>9928.889999999999</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000429</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000119</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3146,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>26-LW-000065</t>
+          <t>25-LW-000429</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000065)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000429)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>47251.64</v>
+        <v>47357.27</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>9450.33</v>
+        <v>9471.450000000001</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000065</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000429</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3268,12 +3268,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>23-CA-017541</t>
+          <t>26-LW-000065</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Riffey, Carolyn E</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000065)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>42527.06</v>
+        <v>47251.64</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>8505.41</v>
+        <v>9450.33</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3327,52 +3327,52 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-017541</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-017541</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000065</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21-CA-005559</t>
+          <t>23-CA-017541</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LOMOGLIO, KAREN</t>
+          <t>Riffey, Carolyn E</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>39392.5</v>
+        <v>42527.06</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>7878.5</v>
+        <v>8505.41</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3454,17 +3454,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=21-CA-005559</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=23-CA-017541</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-005559</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-017541</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3512,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26-LW-000468</t>
+          <t>21-CA-005559</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000468)</t>
+          <t>LOMOGLIO, KAREN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>34957.15</v>
+        <v>39392.5</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>6991.43</v>
+        <v>7878.5</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3571,52 +3571,52 @@
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=21-CA-005559</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000468</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-005559</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3634,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>26-LW-000147</t>
+          <t>26-LW-000727</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000147)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000727)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>34484.85</v>
+        <v>39149.86</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>6896.97</v>
+        <v>7829.97</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000147</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000727</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21-LW-000522</t>
+          <t>26-LW-000468</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 21-LW-000522)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000468)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>34125.04</v>
+        <v>34957.15</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>6825.01</v>
+        <v>6991.43</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 21-LW-000522</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000468</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3878,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26-LW-000447</t>
+          <t>26-LW-000147</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000447)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000147)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>30869.06</v>
+        <v>34484.85</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>6173.81</v>
+        <v>6896.97</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000447</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000147</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4000,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22-LW-000082</t>
+          <t>21-LW-000522</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 22-LW-000082)</t>
+          <t>Tax Deed Titleholder of Record (File 21-LW-000522)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>30182.05</v>
+        <v>34125.04</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>6036.41</v>
+        <v>6825.01</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 22-LW-000082</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 21-LW-000522</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21-CA-004936</t>
+          <t>26-LW-000447</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vega, Luis Orlando</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000447)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>29749.43</v>
+        <v>30869.06</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5949.89</v>
+        <v>6173.81</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -4181,52 +4181,52 @@
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=21-CA-004936</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-004936</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000447</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4244,12 +4244,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23-LW-001012</t>
+          <t>22-LW-000082</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 23-LW-001012)</t>
+          <t>Tax Deed Titleholder of Record (File 22-LW-000082)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>29678.67</v>
+        <v>30182.05</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5935.73</v>
+        <v>6036.41</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 23-LW-001012</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 22-LW-000082</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23-CA-014882</t>
+          <t>21-CA-004936</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Reid, Morris Anthony</t>
+          <t>Vega, Luis Orlando</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>24750</v>
+        <v>29749.43</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4404,16 +4404,16 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>4950</v>
+        <v>5949.89</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Tier 2: Medium Value ($10k-$25k)</t>
+          <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -4430,17 +4430,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-014882</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=21-CA-004936</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-014882</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 21-CA-004936</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26-LW-000585</t>
+          <t>23-LW-001012</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000585)</t>
+          <t>Tax Deed Titleholder of Record (File 23-LW-001012)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>23777.45</v>
+        <v>29678.67</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -4526,16 +4526,16 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4755.49</v>
+        <v>5935.73</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Tier 2: Medium Value ($10k-$25k)</t>
+          <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000585</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 23-LW-001012</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4610,12 +4610,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>25-LW-000404</t>
+          <t>26-LW-000725</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000404)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000725)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>22389.16</v>
+        <v>26584.91</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -4648,16 +4648,16 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4477.83</v>
+        <v>5316.98</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Tier 2: Medium Value ($10k-$25k)</t>
+          <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000404</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000725</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4732,12 +4732,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26-LW-000462</t>
+          <t>23-CA-014882</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000462)</t>
+          <t>Reid, Morris Anthony</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>21981.08</v>
+        <v>24750</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>4396.22</v>
+        <v>4950</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -4791,52 +4791,52 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=23-CA-014882</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000462</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-014882</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26-LW-000702</t>
+          <t>26-LW-000585</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000702)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000585)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>20975.22</v>
+        <v>23777.45</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4195.04</v>
+        <v>4755.49</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000702</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000585</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -4976,12 +4976,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26-LW-000443</t>
+          <t>25-LW-000404</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000443)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000404)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>19884.83</v>
+        <v>22389.16</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3976.97</v>
+        <v>4477.83</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000443</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000404</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5098,12 +5098,12 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26-CA-000549</t>
+          <t>26-LW-000462</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ARRIOLA, CINDY</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000462)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>19279.69</v>
+        <v>21981.08</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>3855.94</v>
+        <v>4396.22</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -5157,52 +5157,52 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=26-CA-000549</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-000549</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000462</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5220,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26-LW-000487</t>
+          <t>26-LW-000702</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000487)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000702)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>18986.52</v>
+        <v>20975.22</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>3797.3</v>
+        <v>4195.04</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000487</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000702</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5342,12 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>25-CA-002135</t>
+          <t>26-LW-000443</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chandler, Matthew B</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000443)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>14603.48</v>
+        <v>19884.83</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>2920.7</v>
+        <v>3976.97</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -5401,52 +5401,52 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=25-CA-002135</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-002135</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000443</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5464,12 +5464,12 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22-CA-008602</t>
+          <t>26-CA-000549</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PORTO , CURRAN KIM</t>
+          <t>ARRIOLA, CINDY</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>14460.18</v>
+        <v>19279.69</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>2892.04</v>
+        <v>3855.94</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -5528,17 +5528,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=22-CA-008602</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=26-CA-000549</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-008602</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-000549</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5586,12 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>25-LW-000342</t>
+          <t>26-LW-000487</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000342)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000487)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5616,7 +5616,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>13694.79</v>
+        <v>18986.52</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>2738.96</v>
+        <v>3797.3</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000342</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000487</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5708,12 +5708,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>25-LW-000397</t>
+          <t>25-CA-002135</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000397)</t>
+          <t>Chandler, Matthew B</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>12322.8</v>
+        <v>14603.48</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2464.56</v>
+        <v>2920.7</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -5767,52 +5767,52 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=25-CA-002135</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000397</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-002135</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5830,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>25-LW-000531</t>
+          <t>22-CA-008602</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000531)</t>
+          <t>PORTO , CURRAN KIM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>11561.97</v>
+        <v>14460.18</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>2312.39</v>
+        <v>2892.04</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -5889,52 +5889,52 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=22-CA-008602</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000531</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-008602</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>25-LW-000252</t>
+          <t>25-LW-000342</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000252)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000342)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>10573.8</v>
+        <v>13694.79</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>2114.76</v>
+        <v>2738.96</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000252</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000342</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26-CA-007844</t>
+          <t>25-LW-000397</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KOLINSKI, KEVIN</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000397)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>10500</v>
+        <v>12322.8</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>2100</v>
+        <v>2464.56</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -6133,52 +6133,52 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=26-CA-007844</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-007844</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000397</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6196,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18-CA-007512</t>
+          <t>25-LW-000531</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kinkoff, Richard R</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000531)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>10000</v>
+        <v>11561.97</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2000</v>
+        <v>2312.39</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -6255,52 +6255,52 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=18-CA-007512</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 18-CA-007512</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000531</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6318,12 +6318,12 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>25-LW-000118</t>
+          <t>25-LW-000252</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000118)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000252)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>9921.51</v>
+        <v>10573.8</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -6356,16 +6356,16 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1984.3</v>
+        <v>2114.76</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000118</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000252</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>25-LW-000549</t>
+          <t>26-CA-007844</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000549)</t>
+          <t>KOLINSKI, KEVIN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6470,7 +6470,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>7627.26</v>
+        <v>10500</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -6478,16 +6478,16 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1525.45</v>
+        <v>2100</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
@@ -6499,52 +6499,52 @@
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=26-CA-007844</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000549</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 26-CA-007844</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6562,12 +6562,12 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>09-CA-009881</t>
+          <t>18-CA-007512</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MULLIS, LISA</t>
+          <t>Kinkoff, Richard R</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>7402.89</v>
+        <v>10000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6600,16 +6600,16 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1480.58</v>
+        <v>2000</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+          <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
@@ -6626,17 +6626,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=09-CA-009881</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=18-CA-007512</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 09-CA-009881</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 18-CA-007512</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>24-CA-000685</t>
+          <t>25-LW-000118</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ERCHID , OMAR A</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000118)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>6447.5</v>
+        <v>9921.51</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1289.5</v>
+        <v>1984.3</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -6743,52 +6743,52 @@
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=24-CA-000685</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-000685</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000118</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>25-LW-000564</t>
+          <t>25-LW-000549</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 25-LW-000564)</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000549)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>5944.21</v>
+        <v>7627.26</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>1188.84</v>
+        <v>1525.45</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000564</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000549</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -6928,12 +6928,12 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>24-CA-005012</t>
+          <t>09-CA-009881</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MURILLO, ANGELA</t>
+          <t>MULLIS, LISA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>5681.72</v>
+        <v>7402.89</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1136.34</v>
+        <v>1480.58</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -6992,17 +6992,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=24-CA-005012</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=09-CA-009881</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-005012</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 09-CA-009881</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>26-LW-000404</t>
+          <t>24-CA-000685</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000404)</t>
+          <t>ERCHID , OMAR A</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>5223.53</v>
+        <v>6447.5</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1044.71</v>
+        <v>1289.5</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -7109,52 +7109,52 @@
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
-          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/taxdeeds</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=24-CA-000685</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000404</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-000685</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Tax Deed Surplus</t>
+          <t>Foreclosure Surplus</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>TAX_DEED</t>
+          <t>FORECLOSURE</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7172,12 +7172,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>23-CA-000671</t>
+          <t>25-LW-000564</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DENNIS HERNANDEZ &amp; ASSOCIATES, P.A</t>
+          <t>Tax Deed Titleholder of Record (File 25-LW-000564)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>3807.59</v>
+        <v>5944.21</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>761.52</v>
+        <v>1188.84</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -7231,52 +7231,52 @@
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=23-CA-000671</t>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-000671</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 25-LW-000564</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 45.032</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Foreclosure Surplus</t>
+          <t>Tax Deed Surplus</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>FORECLOSURE</t>
+          <t>TAX_DEED</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7294,12 +7294,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22-CA-007538</t>
+          <t>24-CA-005012</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Holcomb, Christopher</t>
+          <t>MURILLO, ANGELA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>2905</v>
+        <v>5681.72</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>581</v>
+        <v>1136.34</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -7358,17 +7358,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=22-CA-007538</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=24-CA-005012</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-007538</t>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 24-CA-005012</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:35Z</t>
+          <t>2026-10-31T10:21:03Z</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7416,12 +7416,12 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26-LW-000450</t>
+          <t>26-LW-000404</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tax Deed Titleholder of Record (File 26-LW-000450)</t>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000404)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>2652.06</v>
+        <v>5223.53</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>530.41</v>
+        <v>1044.71</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000450</t>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000404</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-30T10:50:33Z</t>
+          <t>2026-10-31T10:21:02Z</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:50:47</t>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7538,12 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>25-CA-005347</t>
+          <t>23-CA-000671</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kennedy, Willa Helen</t>
+          <t>DENNIS HERNANDEZ &amp; ASSOCIATES, P.A</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>2546</v>
+        <v>3807.59</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>509.2</v>
+        <v>761.52</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -7602,47 +7602,413 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf#search=25-CA-005347</t>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=23-CA-000671</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 23-CA-000671</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:21:03Z</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:21:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22-CA-007538</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Holcomb, Christopher</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>2905</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>581</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Confirm window with clerk</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=22-CA-007538</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 22-CA-007538</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:21:03Z</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:21:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>26-LW-000450</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Tax Deed Titleholder of Record (File 26-LW-000450)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Hillsborough County Tax Deed Registry Parcel, Tampa, FL</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>2652.06</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>530.41</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Confirm window with clerk</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>120 days from clerk's notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/taxdeeds</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Listed on Hillsborough Clerk Weekly Tax Deed Surplus Spreadsheet under Case 26-LW-000450</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/documents/d/guest/copy-of-weekly-tax-deed-spreadsheet-25-10-10-xlsx?download=true</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:21:02Z</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:21:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>25-CA-005347</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Kennedy, Willa Helen</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Hillsborough County Circuit Civil Registry, Tampa, FL</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>2546</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>509.2</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tier 3: Standard Value ($2.5k-$10k)</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Confirm window with clerk</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Claim with clerk per Fla. Stat. § 45.032 — confirm certificate of disbursements date</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf#search=25-CA-005347</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
           <t>Listed on Hillsborough Clerk Court Registry Balances PDF — Case 25-CA-005347</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Thu_10_29_2026.pdf</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>https://publicrec.hillsclerk.com/Civil/registry_trust_balances/Registry_and_TrustAccounts_Balances_as_of_Fri_10_30_2026.pdf</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
         <is>
           <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>Foreclosure Surplus</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>FORECLOSURE</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-10-30T10:50:35Z</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>2026-10-30 10:50:47</t>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-31T10:21:03Z</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:21:14</t>
         </is>
       </c>
     </row>
